--- a/case_study_results/validation_Baxter/Annotator_2/validation_paths_annotated_A2.xlsx
+++ b/case_study_results/validation_Baxter/Annotator_2/validation_paths_annotated_A2.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="301">
   <si>
     <t xml:space="preserve">Path ID</t>
   </si>
@@ -373,7 +373,7 @@
     <t xml:space="preserve">CWE-287|T1134|T1134|CAPEC-633</t>
   </si>
   <si>
-    <t xml:space="preserve">In the reference documents there is source describes tokens being stolen or impersonated. D0006 only mentions an authentication token in the message header, with no weakness.</t>
+    <t xml:space="preserve">In the reference documents there is no source that describes tokens being stolen or impersonated. D0006 only mentions an authentication token in the message header, with no weakness.</t>
   </si>
   <si>
     <t xml:space="preserve">WBM runs Digi Net+OS (D0004), not an OS with access tokens.This doesn't mean this path is impossible.</t>
@@ -929,9 +929,6 @@
   </si>
   <si>
     <t xml:space="preserve">One row per distinct source document referenced anywhere in this dataset.  Tag is whatever tag reference data carries for that URL. it describes the document itself, not any one path.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strong evidence that the same attack behaviour/path occurred, or was documented, for this device/path.</t>
   </si>
 </sst>
 </file>
@@ -1041,6 +1038,7 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="11">
@@ -4452,7 +4450,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B1048576"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
@@ -4473,7 +4471,7 @@
       </c>
       <c r="B2" s="39"/>
     </row>
-    <row r="3" customFormat="false" ht="26.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="40" t="s">
         <v>29</v>
       </c>
@@ -4540,35 +4538,18 @@
       <c r="B12" s="39"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="37" t="s">
-        <v>290</v>
-      </c>
-      <c r="B15" s="37" t="s">
-        <v>291</v>
-      </c>
+      <c r="A15" s="38"/>
+      <c r="B15" s="39"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="38" t="s">
-        <v>292</v>
-      </c>
+      <c r="A16" s="40"/>
       <c r="B16" s="39"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="40" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="39" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="B18" s="39" t="s">
-        <v>294</v>
-      </c>
-    </row>
+      <c r="A17" s="40"/>
+      <c r="B17" s="39"/>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
